--- a/reports/עסקים חשודים מהאינטרנט 03.07.2026.xlsx
+++ b/reports/עסקים חשודים מהאינטרנט 03.07.2026.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="עסקים" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="עסקים בירושלים" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,8 +31,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +46,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1ECF1"/>
+        <bgColor rgb="00D1ECF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,30 +83,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="001F4E79"/>
-      </left>
-      <right style="thin">
-        <color rgb="001F4E79"/>
-      </right>
-      <top style="thin">
-        <color rgb="001F4E79"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="001F4E79"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -444,22 +486,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>שם העסק</t>
@@ -467,335 +503,369 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>סוג העסק</t>
+          <t>כתובת</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>כתובת</t>
+          <t>סוג עסק</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>דירוג חשד</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>כתובת תואמת (מהעירייה)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>שמות בעלי נכסים</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>מס' דירות</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>פירוט החשד</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>סיבת אי-חשד</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>מקור המידע (URL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>קישור למקור</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>אבו ננה אחמד</t>
+          <t>מרכז לשרותי בריאות וקהילה</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>בניית בתים חד-משפחתיים</t>
+          <t>אבינדב 2</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>אבו זיד אל-הילאל 11</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>אבו זיד אל-הילאל 11</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dunsguide.co.il/Cb9c55068b6a5e8f2cdb2157b2dbd1a38_%D7%97%D7%91%D7%A8%D7%95%D7%AA_%D7%91%D7%A0%D7%99%D7%94_%D7%95%D7%A0%D7%93%D7%9C%D7%9F/%D7%90%D7%91%D7%95_%D7%A0%D7%A0%D7%94_%D7%90%D7%97%D7%9E%D7%93</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>קופת חולים / שירותי בריאות</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/21355490/32060</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>אלקצאר שירות בריאות בע"מ</t>
+          <t>מרפאה משה הופמן תרפיות</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>מרפאה עצמאית</t>
+          <t>אבינועם ילין 13</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>אבו רביע 18</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>אבו רביע 18</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.clalit.co.il/he/sefersherut/pages/clinicdetails.aspx?ddeptcode=14630</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>מרפאה / פיזיותרפיה</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.clalit.co.il/he/sefersherut/pages/doctordetails.aspx?edeptcode=988052269&amp;eservicecode=161000&amp;employeeid=BCCB8A3341815823F3E8410EBE0E7EC5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>אל אקצא - בית מרקחת</t>
+          <t>לאומית שירותי בריאות ירושלים</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>בית מרקחת</t>
+          <t>אביתר הכהן 1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>אבו רביע 18</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>אבו רביע 18</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.clalit.co.il/he/sefersherut/pages/pharmacydetails.aspx?ddeptcode=19075</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>קופת חולים</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/34212600/43950</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>האחים קליניס בע"מ</t>
+          <t>דניאל קאהן - מעסה רפואי בכיר</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ניקיון משרדים</t>
+          <t>אבן שמואל 37</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>אבולעפיה 2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>אבולעפיה 2</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dunsguide.co.il/Ccb515ad66658baa565d2d5e40b70eca4_%D7%A0%D7%99%D7%A7%D7%99%D7%95%D7%9F_%D7%9E%D7%A9%D7%A8%D7%93%D7%99%D7%9D/%D7%94%D7%90%D7%97%D7%99%D7%9D_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>טיפול גוף / רפואה משלימה</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80364123/40030046</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>עובד - שרותי ניקיון בע"מ</t>
+          <t>רון הרן</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ניקיון משרדים</t>
+          <t>אבן שפרוט 16</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>אבולעפיה 2</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>אבולעפיה 2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dunsguide.co.il/C806a38831371870e93d1685b9caa4764_%D7%A0%D7%99%D7%A7%D7%99%D7%95%D7%9F_%D7%9E%D7%A9%D7%A8%D7%93%D7%99%D7%9D/%D7%A2%D7%95%D7%91%D7%93_%D7%A9%D7%A8%D7%95%D7%AA%D7%99_%D7%A0%D7%99%D7%A7%D7%99%D7%95%D7%9F</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>משרד פרסום</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.dunsguide.co.il/Ca084ce5b1147b3832bee5cdafa9cca9a_%D7%9E%D7%A9%D7%A8%D7%93%D7%99_%D7%A4%D7%A8%D7%A1%D7%95%D7%9D/%D7%A8%D7%95%D7%9F_%D7%94%D7%A8%D7%9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>שטרודל נקודה קום בע"מ</t>
+          <t>פוגל יורם</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>חברות היי-טק ומחשוב</t>
+          <t>אבן שפרוט 16</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>אבולעפיה 30</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>אבולעפיה 30</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dunsguide.co.il/C66930156e7ddd847edf910e6deaa2f0f_%D7%97%D7%91%D7%A8%D7%95%D7%AA_%D7%94%D7%99%D7%98%D7%A7_%D7%95%D7%9E%D7%99%D7%97%D7%A9%D7%95%D7%91/%D7%A9%D7%98%D7%A8%D7%95%D7%93%D7%9C_%D7%A0%D7%A7%D7%95%D7%93%D7%94_%D7%A7%D7%95%D7%9D</t>
+          <t>אדריכלים</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/6018720/630</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>אפשטיין ושות' משרד עו"ד</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>אלפסי 28</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>משרד עורכי דין</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80256202/9010118</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>זילברמן אליעזר</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>אלפסי 9</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>משרד רואי חשבון</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/16448300/46140</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>משכן לבטח בע"מ</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>אלפסי 35</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>שיפוצים ותיקונים</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80314169/48570</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>עומר געש</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ארלוזורוב 5</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>גרפיקאים / עיצוב</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80070036/11301</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>גנענע</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>בורוכוב 12</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>שירותי גינון</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80010504/11000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>נגיעה בעץ</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>בורוכוב 22</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>פרגולות / נגרות</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80163803/40480</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>חשמל עמיהוד</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>בורוכוב 30</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>חשמלאים</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80029577/17910</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>פולישוק דניאל - ייעוץ בנקאי</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>בורוכוב 58</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>ייעוץ פיננסי / בנקאי</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80336727/19770</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>ד"ר פליישמן צבי</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>בורוכוב 60</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>מרפאה וטרינרית</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/33125270/14670</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>נגיעה בעץ</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>בורוכוב 60</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>פרגולות / נגרות</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/64276600/40480</t>
         </is>
       </c>
     </row>

--- a/reports/עסקים חשודים מהאינטרנט 03.07.2026.xlsx
+++ b/reports/עסקים חשודים מהאינטרנט 03.07.2026.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="עסקים" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="עסקים חשודים" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,8 +28,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -41,11 +39,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,31 +52,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="001F4E79"/>
-      </left>
-      <right style="thin">
-        <color rgb="001F4E79"/>
-      </right>
-      <top style="thin">
-        <color rgb="001F4E79"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="001F4E79"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -445,21 +430,21 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>שם העסק</t>
@@ -514,17 +499,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>אבו ננה אחמד</t>
+          <t>שמואל לבן משרד עו"ד</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>בניית בתים חד-משפחתיים</t>
+          <t>משרד עורכי דין</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>אבו זיד אל-הילאל 11</t>
+          <t>אבנר גרשון 12, ירושלים</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -534,7 +519,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>אבו זיד אל-הילאל 11</t>
+          <t>אבנר גרשון 12, ירושלים</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -555,24 +540,24 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>https://www.dunsguide.co.il/Cb9c55068b6a5e8f2cdb2157b2dbd1a38_%D7%97%D7%91%D7%A8%D7%95%D7%AA_%D7%91%D7%A0%D7%99%D7%94_%D7%95%D7%A0%D7%93%D7%9C%D7%9F/%D7%90%D7%91%D7%95_%D7%A0%D7%A0%D7%94_%D7%90%D7%97%D7%9E%D7%93</t>
+          <t>https://www.d.co.il/80380033/9010106</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>אלקצאר שירות בריאות בע"מ</t>
+          <t>ביסמוט - מערכות עיתונים</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>מרפאה עצמאית</t>
+          <t>מערכות עיתונים</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>אבו רביע 18</t>
+          <t>אבנר גרשון 12, ירושלים</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -582,7 +567,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>אבו רביע 18</t>
+          <t>אבנר גרשון 12, ירושלים</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -603,24 +588,24 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>https://www.clalit.co.il/he/sefersherut/pages/clinicdetails.aspx?ddeptcode=14630</t>
+          <t>https://www.b144.co.il/b144_sip/401C041341756D5B4C160615</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>אל אקצא - בית מרקחת</t>
+          <t>פויכטונגר דינה</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>בית מרקחת</t>
+          <t>טיפול נפשי / פסיכולוגיה</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>אבו רביע 18</t>
+          <t>אברבנאל 15, ירושלים</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -630,7 +615,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>אבו רביע 18</t>
+          <t>אברבנאל 15, ירושלים</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -651,24 +636,24 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>https://www.clalit.co.il/he/sefersherut/pages/pharmacydetails.aspx?ddeptcode=19075</t>
+          <t>https://www.d.co.il/80132191/40230</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>האחים קליניס בע"מ</t>
+          <t>מרכז התרגום ישראל בע"מ</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ניקיון משרדים</t>
+          <t>שירותי תרגום</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>אבולעפיה 2</t>
+          <t>אברבנאל 32, ירושלים</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -678,7 +663,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>אבולעפיה 2</t>
+          <t>אברבנאל 32, ירושלים</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -699,24 +684,24 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>https://www.dunsguide.co.il/Ccb515ad66658baa565d2d5e40b70eca4_%D7%A0%D7%99%D7%A7%D7%99%D7%95%D7%9F_%D7%9E%D7%A9%D7%A8%D7%93%D7%99%D7%9D/%D7%94%D7%90%D7%97%D7%99%D7%9D_%D7%A7%D7%9C%D7%99%D7%A0%D7%99%D7%A1</t>
+          <t>https://www.d.co.il/21390460/51870</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>עובד - שרותי ניקיון בע"מ</t>
+          <t>שירותי רפואה ופיזיותרפיה</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ניקיון משרדים</t>
+          <t>רפואה / פיזיותרפיה</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>אבולעפיה 2</t>
+          <t>אגריפס 6, ירושלים</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -726,7 +711,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>אבולעפיה 2</t>
+          <t>אגריפס 6, ירושלים</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -747,24 +732,24 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>https://www.dunsguide.co.il/C806a38831371870e93d1685b9caa4764_%D7%A0%D7%99%D7%A7%D7%99%D7%95%D7%9F_%D7%9E%D7%A9%D7%A8%D7%93%D7%99%D7%9D/%D7%A2%D7%95%D7%91%D7%93_%D7%A9%D7%A8%D7%95%D7%AA%D7%99_%D7%A0%D7%99%D7%A7%D7%99%D7%95%D7%9F</t>
+          <t>https://www.clalit.co.il/he/sefersherut/pages/clinicdetails.aspx?ddeptcode=998788</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>שטרודל נקודה קום בע"מ</t>
+          <t>מרפאת מכון בדיקות ירושלים</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>חברות היי-טק ומחשוב</t>
+          <t>מרפאה / מכון בדיקות</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>אבולעפיה 30</t>
+          <t>אגריפס 6, ירושלים</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -774,7 +759,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>אבולעפיה 30</t>
+          <t>אגריפס 6, ירושלים</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -795,7 +780,7 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>https://www.dunsguide.co.il/C66930156e7ddd847edf910e6deaa2f0f_%D7%97%D7%91%D7%A8%D7%95%D7%AA_%D7%94%D7%99%D7%98%D7%A7_%D7%95%D7%9E%D7%99%D7%97%D7%A9%D7%95%D7%91/%D7%A9%D7%98%D7%A8%D7%95%D7%93%D7%9C_%D7%A0%D7%A7%D7%95%D7%93%D7%94_%D7%A7%D7%95%D7%9D</t>
+          <t>https://www.doctorim.co.il/clinic-10025163/</t>
         </is>
       </c>
     </row>
